--- a/system_development/Damascus/V0.5.1/software development/thermal_optical/iteration_25/data/Test_Notes.xlsx
+++ b/system_development/Damascus/V0.5.1/software development/thermal_optical/iteration_25/data/Test_Notes.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\LPBF-Observer\system_development\Damascus\V0.5.1\software development\thermal_optical\iteration_25\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/killedar_email_sc_edu/Documents/GitHub/LPBF-Observer/system_development/Damascus/V0.5.1/software development/thermal_optical/iteration_25/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D575441-1B28-4CCD-9DCB-C60EF4194AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7D575441-1B28-4CCD-9DCB-C60EF4194AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85025598-56C4-4A8C-9C32-BE565178E006}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test 1" sheetId="2" r:id="rId1"/>
     <sheet name="Test 2" sheetId="1" r:id="rId2"/>
     <sheet name="Test 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="32">
   <si>
     <t>Optical</t>
   </si>
@@ -120,6 +121,9 @@
   </si>
   <si>
     <t>~850 MB</t>
+  </si>
+  <si>
+    <t>FPS</t>
   </si>
 </sst>
 </file>
@@ -215,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,12 +261,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -630,14 +628,14 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="17">
+      <c r="A7" s="16"/>
+      <c r="B7" s="15">
         <v>361959</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="C7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="15">
         <v>19</v>
       </c>
     </row>
@@ -1331,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5FEC126-2F26-48A3-B7D6-88E98B0D6764}">
-  <dimension ref="A2:J22"/>
+  <dimension ref="A2:J24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.88671875" style="1"/>
@@ -1376,11 +1374,11 @@
       <c r="D3" s="10">
         <v>19</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="15"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1"/>
       <c r="I3" t="s">
         <v>18</v>
       </c>
@@ -1399,11 +1397,11 @@
       <c r="D4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="15"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="1"/>
       <c r="I4" t="s">
         <v>19</v>
       </c>
@@ -1749,22 +1747,22 @@
       <c r="A21" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="15">
         <v>676406</v>
       </c>
-      <c r="C21" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="17">
+      <c r="C21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="15">
         <v>676406</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="17" t="s">
+      <c r="F21" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="15" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1784,6 +1782,458 @@
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C67E8557-9FA4-45B6-97EC-B39A1D74472C}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="3"/>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="9">
+        <v>573</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="9">
+        <v>18997</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="10">
+        <v>19</v>
+      </c>
+      <c r="E4" s="9">
+        <v>18997</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="9">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="15">
+        <v>676406</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="15">
+        <v>676406</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1" t="s">
         <v>30</v>
       </c>
     </row>
